--- a/Uploaded_Bot_Backtest.xlsx
+++ b/Uploaded_Bot_Backtest.xlsx
@@ -6610,7 +6610,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fill  — over 90 days no retrace bar's extreme landed exactly on the zone midpoint to float precision, so touch and trade-through selected the same fills. The bug is real and would bite on tick-quantised or round-number levels; on this sample it cost nothing.</t>
+          <t xml:space="preserve">  fill  — an exact touch (bar extreme equal to the zone midpoint to float precision) does occur in this data: 1,336 times across 409,112 bar/zone pairs, about 0.33%. It simply never landed on the FIRST qualifying retrace bar of an actual signal. At ~70 trades x 8 retrace bars the expected number of affected trades is only 1-2, so measuring zero here is the luck of the draw, NOT evidence the bug is harmless. On a tick-quantised feed or around round numbers it would bite. Treat this row as 'not measurable on this sample', not 'costless'.</t>
         </is>
       </c>
     </row>
